--- a/Documentation/Working_Documents/Chatterbox_BOM.xlsx
+++ b/Documentation/Working_Documents/Chatterbox_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://neilsquiresoc.sharepoint.com/sites/MMC-RD/Shared Documents/RD 24-11 Auditory Scanning Device/Auditory_Scanning_Device/Documentation/Working_Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://neilsquiresoc-my.sharepoint.com/personal/stephand_neilsquire_ca/Documents/Documents/GitHub/Auditory-Scanning-Device/Documentation/Working_Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="723" documentId="11_DC0E2523FAFE28515E8D5C5A1D4A6B02C3B15AFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A5F0AB9-1B7B-4065-9A23-2D02FAE5772A}"/>
+  <xr:revisionPtr revIDLastSave="809" documentId="11_DC0E2523FAFE28515E8D5C5A1D4A6B02C3B15AFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE5F92A-1582-4439-BD86-02DFDF131276}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="138">
   <si>
     <t>Total filament (g)</t>
   </si>
@@ -296,33 +296,12 @@
     <t>Battery Cover</t>
   </si>
   <si>
-    <t>2h17m</t>
-  </si>
-  <si>
-    <t>2h49m</t>
-  </si>
-  <si>
-    <t>2h32m</t>
-  </si>
-  <si>
     <t>31m (each)</t>
   </si>
   <si>
-    <t>41m (each)</t>
-  </si>
-  <si>
-    <t>27m (each)</t>
-  </si>
-  <si>
     <t>22m (each)</t>
   </si>
   <si>
-    <t>49m (each)</t>
-  </si>
-  <si>
-    <t>20m</t>
-  </si>
-  <si>
     <t>Soldering Iron</t>
   </si>
   <si>
@@ -435,6 +414,42 @@
   </si>
   <si>
     <t>https://www.digikey.ca/en/products/detail/sullins-connector-solutions/PPTC081LFBN-RC/810147</t>
+  </si>
+  <si>
+    <t>27m</t>
+  </si>
+  <si>
+    <t>37m (each)</t>
+  </si>
+  <si>
+    <t>28m (each)</t>
+  </si>
+  <si>
+    <t>47m (each)</t>
+  </si>
+  <si>
+    <t>2h44m</t>
+  </si>
+  <si>
+    <t>2h29m</t>
+  </si>
+  <si>
+    <t>2h14m</t>
+  </si>
+  <si>
+    <t>2h6m</t>
+  </si>
+  <si>
+    <t>Slide Switch Cover</t>
+  </si>
+  <si>
+    <t>Slide Switch Cover Pin</t>
+  </si>
+  <si>
+    <t>9m (each)</t>
+  </si>
+  <si>
+    <t>7m (each)</t>
   </si>
 </sst>
 </file>
@@ -1182,26 +1197,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EE8AD1-7DB5-46E4-9BCF-A08DFBDA7B00}">
-  <dimension ref="A1:N72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N74"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.453125" customWidth="1"/>
-    <col min="13" max="13" width="17.26953125" customWidth="1"/>
-    <col min="14" max="14" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="35.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:14" ht="36" x14ac:dyDescent="0.65">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1217,7 +1232,7 @@
       <c r="I1" s="75"/>
       <c r="J1" s="75"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1225,7 +1240,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1233,7 +1248,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I4" s="58" t="s">
         <v>0</v>
       </c>
@@ -1248,26 +1263,26 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="I5" s="59">
         <f>SUM(H40:H45)</f>
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="J5" s="55"/>
       <c r="K5" s="56">
         <f>K6+K31+K38</f>
-        <v>135.54399999999998</v>
+        <v>134.31899999999999</v>
       </c>
       <c r="L5" s="57">
         <f>L6+L31+L38</f>
-        <v>166.42000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>167.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1287,13 +1302,13 @@
         <v>109.86899999999999</v>
       </c>
       <c r="L6" s="7">
-        <f>SUM(L8:L38)</f>
-        <v>108.74499999999999</v>
+        <f>SUM(L8:L30)</f>
+        <v>110.87999999999998</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>2</v>
@@ -1302,7 +1317,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
@@ -1333,7 +1348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="B8" s="19" t="s">
         <v>41</v>
@@ -1364,15 +1379,15 @@
         <v>11.07</v>
       </c>
       <c r="L8" s="20">
-        <f t="shared" ref="L8" si="2">I8*J8</f>
+        <f t="shared" ref="L8:L30" si="2">I8*J8</f>
         <v>11.07</v>
       </c>
       <c r="M8" s="70"/>
       <c r="N8" s="74" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
       <c r="B9" s="19" t="s">
         <v>42</v>
@@ -1401,13 +1416,16 @@
         <f t="shared" si="1"/>
         <v>6.13</v>
       </c>
-      <c r="L9" s="20"/>
+      <c r="L9" s="20">
+        <f t="shared" si="2"/>
+        <v>6.13</v>
+      </c>
       <c r="M9" s="68"/>
       <c r="N9" s="74" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="19" t="s">
         <v>43</v>
@@ -1436,13 +1454,16 @@
         <f t="shared" si="1"/>
         <v>6.13</v>
       </c>
-      <c r="L10" s="20"/>
+      <c r="L10" s="20">
+        <f t="shared" si="2"/>
+        <v>6.13</v>
+      </c>
       <c r="M10" s="68"/>
       <c r="N10" s="74" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="B11" s="19" t="s">
         <v>44</v>
@@ -1471,13 +1492,16 @@
         <f t="shared" si="1"/>
         <v>2.65</v>
       </c>
-      <c r="L11" s="20"/>
+      <c r="L11" s="20">
+        <f t="shared" si="2"/>
+        <v>2.65</v>
+      </c>
       <c r="M11" s="68"/>
       <c r="N11" s="74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="19" t="s">
         <v>45</v>
@@ -1506,13 +1530,16 @@
         <f t="shared" si="1"/>
         <v>10.93</v>
       </c>
-      <c r="L12" s="20"/>
+      <c r="L12" s="20">
+        <f t="shared" si="2"/>
+        <v>10.93</v>
+      </c>
       <c r="M12" s="68"/>
       <c r="N12" s="74" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="19"/>
       <c r="B13" s="19" t="s">
         <v>46</v>
@@ -1541,13 +1568,16 @@
         <f t="shared" si="1"/>
         <v>7.69</v>
       </c>
-      <c r="L13" s="20"/>
+      <c r="L13" s="20">
+        <f t="shared" si="2"/>
+        <v>7.69</v>
+      </c>
       <c r="M13" s="68"/>
       <c r="N13" s="74" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
       <c r="B14" s="19" t="s">
         <v>47</v>
@@ -1576,13 +1606,16 @@
         <f t="shared" si="1"/>
         <v>12.35</v>
       </c>
-      <c r="L14" s="20"/>
+      <c r="L14" s="20">
+        <f t="shared" si="2"/>
+        <v>12.35</v>
+      </c>
       <c r="M14" s="68"/>
       <c r="N14" s="74" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
       <c r="B15" s="19" t="s">
         <v>48</v>
@@ -1611,13 +1644,16 @@
         <f t="shared" si="1"/>
         <v>2.2799999999999998</v>
       </c>
-      <c r="L15" s="20"/>
+      <c r="L15" s="20">
+        <f t="shared" si="2"/>
+        <v>2.2799999999999998</v>
+      </c>
       <c r="M15" s="68"/>
       <c r="N15" s="74" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="19"/>
       <c r="B16" s="19" t="s">
         <v>56</v>
@@ -1646,13 +1682,16 @@
         <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
-      <c r="L16" s="20"/>
+      <c r="L16" s="20">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
       <c r="M16" s="68"/>
       <c r="N16" s="74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="19"/>
       <c r="B17" s="19" t="s">
         <v>49</v>
@@ -1681,13 +1720,16 @@
         <f t="shared" si="1"/>
         <v>4.34</v>
       </c>
-      <c r="L17" s="20"/>
+      <c r="L17" s="20">
+        <f t="shared" si="2"/>
+        <v>4.34</v>
+      </c>
       <c r="M17" s="68"/>
       <c r="N17" s="74" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
         <v>50</v>
@@ -1716,13 +1758,16 @@
         <f t="shared" si="1"/>
         <v>1.48</v>
       </c>
-      <c r="L18" s="20"/>
+      <c r="L18" s="20">
+        <f t="shared" si="2"/>
+        <v>1.48</v>
+      </c>
       <c r="M18" s="68"/>
       <c r="N18" s="74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
         <v>55</v>
@@ -1751,13 +1796,16 @@
         <f t="shared" si="1"/>
         <v>1.92</v>
       </c>
-      <c r="L19" s="20"/>
+      <c r="L19" s="20">
+        <f t="shared" si="2"/>
+        <v>1.92</v>
+      </c>
       <c r="M19" s="68"/>
       <c r="N19" s="74" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
         <v>66</v>
@@ -1786,13 +1834,16 @@
         <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="L20" s="20"/>
+      <c r="L20" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
       <c r="M20" s="68"/>
       <c r="N20" s="74" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="19" t="s">
         <v>67</v>
@@ -1821,16 +1872,19 @@
         <f t="shared" si="1"/>
         <v>2.38</v>
       </c>
-      <c r="L21" s="20"/>
+      <c r="L21" s="20">
+        <f t="shared" si="2"/>
+        <v>2.38</v>
+      </c>
       <c r="M21" s="68"/>
       <c r="N21" s="74" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="19"/>
       <c r="B22" s="19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -1856,23 +1910,26 @@
         <f t="shared" si="1"/>
         <v>7.49</v>
       </c>
-      <c r="L22" s="20"/>
+      <c r="L22" s="20">
+        <f t="shared" si="2"/>
+        <v>7.49</v>
+      </c>
       <c r="M22" s="68"/>
       <c r="N22" s="74" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="19"/>
       <c r="B23" s="19" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F23" s="19" t="s">
         <v>58</v>
@@ -1893,13 +1950,16 @@
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="L23" s="20"/>
+      <c r="L23" s="20">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
       <c r="M23" s="68"/>
       <c r="N23" s="74" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="19"/>
       <c r="B24" s="19" t="s">
         <v>51</v>
@@ -1928,13 +1988,16 @@
         <f t="shared" si="1"/>
         <v>0.86</v>
       </c>
-      <c r="L24" s="20"/>
+      <c r="L24" s="20">
+        <f t="shared" si="2"/>
+        <v>0.86</v>
+      </c>
       <c r="M24" s="68"/>
       <c r="N24" s="74" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="19"/>
       <c r="B25" s="19" t="s">
         <v>52</v>
@@ -1965,13 +2028,16 @@
         <f t="shared" si="1"/>
         <v>12.2</v>
       </c>
-      <c r="L25" s="20"/>
+      <c r="L25" s="20">
+        <f t="shared" si="2"/>
+        <v>12.2</v>
+      </c>
       <c r="M25" s="68"/>
       <c r="N25" s="74" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="19"/>
       <c r="B26" s="19" t="s">
         <v>53</v>
@@ -2000,13 +2066,16 @@
         <f t="shared" si="1"/>
         <v>1.63</v>
       </c>
-      <c r="L26" s="20"/>
+      <c r="L26" s="20">
+        <f t="shared" si="2"/>
+        <v>1.63</v>
+      </c>
       <c r="M26" s="68"/>
       <c r="N26" s="74" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
       <c r="B27" s="19" t="s">
         <v>54</v>
@@ -2035,13 +2104,16 @@
         <f t="shared" si="1"/>
         <v>1.58</v>
       </c>
-      <c r="L27" s="20"/>
+      <c r="L27" s="20">
+        <f t="shared" si="2"/>
+        <v>1.58</v>
+      </c>
       <c r="M27" s="68"/>
       <c r="N27" s="74" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="19"/>
       <c r="B28" s="19" t="s">
         <v>57</v>
@@ -2070,23 +2142,26 @@
         <f t="shared" si="1"/>
         <v>2.42</v>
       </c>
-      <c r="L28" s="20"/>
+      <c r="L28" s="20">
+        <f t="shared" si="2"/>
+        <v>2.42</v>
+      </c>
       <c r="M28" s="68"/>
       <c r="N28" s="74" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="19"/>
       <c r="B29" s="19" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>58</v>
@@ -2107,13 +2182,16 @@
         <f t="shared" si="1"/>
         <v>9.0989999999999984</v>
       </c>
-      <c r="L29" s="20"/>
+      <c r="L29" s="20">
+        <f t="shared" si="2"/>
+        <v>10.11</v>
+      </c>
       <c r="M29" s="68"/>
       <c r="N29" s="74" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19"/>
       <c r="B30" s="19" t="s">
         <v>68</v>
@@ -2142,13 +2220,16 @@
         <f t="shared" si="1"/>
         <v>0.74</v>
       </c>
-      <c r="L30" s="20"/>
+      <c r="L30" s="20">
+        <f t="shared" si="2"/>
+        <v>0.74</v>
+      </c>
       <c r="M30" s="68"/>
       <c r="N30" s="74" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="28"/>
       <c r="B31" s="48" t="s">
         <v>25</v>
@@ -2172,7 +2253,7 @@
       <c r="M31" s="29"/>
       <c r="N31" s="73"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="30"/>
       <c r="B32" s="10" t="s">
         <v>2</v>
@@ -2210,7 +2291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="21"/>
       <c r="B33" s="21" t="s">
         <v>35</v>
@@ -2245,7 +2326,7 @@
       <c r="M33" s="21"/>
       <c r="N33" s="21"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>37</v>
@@ -2279,7 +2360,7 @@
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="21"/>
       <c r="B35" s="21" t="s">
         <v>39</v>
@@ -2313,7 +2394,7 @@
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15" t="s">
@@ -2346,7 +2427,7 @@
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
     </row>
-    <row r="37" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="31"/>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -2362,7 +2443,7 @@
       <c r="M37" s="31"/>
       <c r="N37" s="31"/>
     </row>
-    <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="32"/>
       <c r="B38" s="49" t="s">
         <v>22</v>
@@ -2374,22 +2455,22 @@
       <c r="G38" s="33"/>
       <c r="H38" s="33"/>
       <c r="I38" s="12">
-        <f>SUM(I40:I51)</f>
-        <v>707</v>
+        <f>SUM(I40:I53)</f>
+        <v>658</v>
       </c>
       <c r="J38" s="34"/>
       <c r="K38" s="11">
-        <f>SUM(K40:K51)</f>
-        <v>17.675000000000001</v>
+        <f>SUM(K40:K53)</f>
+        <v>16.450000000000006</v>
       </c>
       <c r="L38" s="11">
-        <f>SUM(L40:L51)</f>
-        <v>17.675000000000001</v>
+        <f>SUM(L40:L53)</f>
+        <v>16.450000000000006</v>
       </c>
       <c r="M38" s="33"/>
       <c r="N38" s="35"/>
     </row>
-    <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="36"/>
       <c r="B39" s="12" t="s">
         <v>2</v>
@@ -2429,7 +2510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="23"/>
       <c r="B40" s="23" t="s">
         <v>77</v>
@@ -2446,29 +2527,29 @@
         <v>1</v>
       </c>
       <c r="H40" s="23">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I40" s="23">
         <f>G40*H40</f>
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J40" s="24">
         <v>25</v>
       </c>
       <c r="K40" s="24">
         <f>IF(G40&gt;0,(J40/1000)*G40*H40,0)</f>
-        <v>2.6500000000000004</v>
+        <v>2.4250000000000003</v>
       </c>
       <c r="L40" s="24">
         <f>K40</f>
-        <v>2.6500000000000004</v>
+        <v>2.4250000000000003</v>
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="16" t="s">
         <v>78</v>
@@ -2485,29 +2566,29 @@
         <v>1</v>
       </c>
       <c r="H41" s="16">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I41" s="16">
         <f t="shared" ref="I41" si="6">G41*H41</f>
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="J41" s="13">
         <v>25</v>
       </c>
       <c r="K41" s="13">
         <f t="shared" ref="K41" si="7">IF(G41&gt;0,(J41/1000)*G41*H41,0)</f>
-        <v>2.7250000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="L41" s="13">
         <f t="shared" ref="L41" si="8">K41</f>
-        <v>2.7250000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="M41" s="16"/>
       <c r="N41" s="16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="16" t="s">
         <v>79</v>
@@ -2524,29 +2605,29 @@
         <v>1</v>
       </c>
       <c r="H42" s="16">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I42" s="16">
-        <f t="shared" ref="I42:I50" si="9">G42*H42</f>
-        <v>89</v>
+        <f t="shared" ref="I42:I52" si="9">G42*H42</f>
+        <v>76</v>
       </c>
       <c r="J42" s="24">
         <v>25</v>
       </c>
       <c r="K42" s="13">
         <f>IF(G42&gt;0,(J42/1000)*G42*H42,0)</f>
-        <v>2.2250000000000001</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="L42" s="13">
         <f>K42</f>
-        <v>2.2250000000000001</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="M42" s="16"/>
       <c r="N42" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="16" t="s">
         <v>76</v>
@@ -2563,29 +2644,29 @@
         <v>1</v>
       </c>
       <c r="H43" s="16">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" si="9"/>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J43" s="13">
         <v>25</v>
       </c>
       <c r="K43" s="13">
         <f>IF(G43&gt;0,(J43/1000)*G43*H43,0)</f>
-        <v>2.15</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="L43" s="13">
         <f>K43</f>
-        <v>2.15</v>
+        <v>1.9000000000000001</v>
       </c>
       <c r="M43" s="16"/>
       <c r="N43" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="16" t="s">
         <v>80</v>
@@ -2621,10 +2702,10 @@
       </c>
       <c r="M44" s="16"/>
       <c r="N44" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="16" t="s">
         <v>81</v>
@@ -2641,29 +2722,29 @@
         <v>4</v>
       </c>
       <c r="H45" s="16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I45" s="16">
         <f t="shared" si="9"/>
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J45" s="24">
         <v>25</v>
       </c>
       <c r="K45" s="13">
-        <f t="shared" ref="K45:K50" si="10">IF(G45&gt;0,(J45/1000)*G45*H45,0)</f>
-        <v>2.6</v>
+        <f t="shared" ref="K45:K52" si="10">IF(G45&gt;0,(J45/1000)*G45*H45,0)</f>
+        <v>2.3000000000000003</v>
       </c>
       <c r="L45" s="13">
-        <f t="shared" ref="L45:L50" si="11">K45</f>
-        <v>2.6</v>
+        <f t="shared" ref="L45:L52" si="11">K45</f>
+        <v>2.3000000000000003</v>
       </c>
       <c r="M45" s="16"/>
       <c r="N45" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="69" t="s">
         <v>82</v>
@@ -2699,10 +2780,10 @@
       </c>
       <c r="M46" s="16"/>
       <c r="N46" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="69" t="s">
         <v>83</v>
@@ -2738,10 +2819,10 @@
       </c>
       <c r="M47" s="16"/>
       <c r="N47" s="16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="69" t="s">
         <v>84</v>
@@ -2758,32 +2839,32 @@
         <v>2</v>
       </c>
       <c r="H48" s="69">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I48" s="69">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J48" s="13">
         <v>25</v>
       </c>
       <c r="K48" s="13">
         <f t="shared" si="10"/>
-        <v>1.2000000000000002</v>
+        <v>1.05</v>
       </c>
       <c r="L48" s="13">
         <f t="shared" si="11"/>
-        <v>1.2000000000000002</v>
+        <v>1.05</v>
       </c>
       <c r="M48" s="16"/>
       <c r="N48" s="16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="37"/>
       <c r="B49" s="71" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C49" s="71"/>
       <c r="D49" s="71" t="s">
@@ -2794,188 +2875,230 @@
         <v>18</v>
       </c>
       <c r="G49" s="71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H49" s="71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="71">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="J49" s="24">
+        <v>4</v>
+      </c>
+      <c r="J49" s="13">
         <v>25</v>
       </c>
       <c r="K49" s="13">
         <f t="shared" si="10"/>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="L49" s="13">
         <f t="shared" si="11"/>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="37"/>
-      <c r="B50" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37" t="s">
+      <c r="B50" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37" t="s">
+      <c r="E50" s="71"/>
+      <c r="F50" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="37">
-        <v>1</v>
-      </c>
-      <c r="H50" s="37">
-        <v>7</v>
-      </c>
-      <c r="I50" s="37">
+      <c r="G50" s="71">
+        <v>4</v>
+      </c>
+      <c r="H50" s="71">
+        <v>1</v>
+      </c>
+      <c r="I50" s="71">
         <f t="shared" si="9"/>
-        <v>7</v>
-      </c>
-      <c r="J50" s="24">
+        <v>4</v>
+      </c>
+      <c r="J50" s="13">
         <v>25</v>
       </c>
       <c r="K50" s="13">
         <f t="shared" si="10"/>
-        <v>0.17500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="L50" s="13">
         <f t="shared" si="11"/>
-        <v>0.17500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" s="66" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="64"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="64"/>
-      <c r="H51" s="64"/>
-      <c r="I51" s="64"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="64"/>
-      <c r="N51" s="64"/>
-    </row>
-    <row r="52" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="38"/>
-      <c r="B52" s="50" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="37"/>
+      <c r="B51" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="71"/>
+      <c r="D51" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="71"/>
+      <c r="F51" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="71">
+        <v>1</v>
+      </c>
+      <c r="H51" s="71">
+        <v>2</v>
+      </c>
+      <c r="I51" s="71">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J51" s="24">
+        <v>25</v>
+      </c>
+      <c r="K51" s="13">
+        <f t="shared" si="10"/>
+        <v>0.05</v>
+      </c>
+      <c r="L51" s="13">
+        <f t="shared" si="11"/>
+        <v>0.05</v>
+      </c>
+      <c r="M51" s="37"/>
+      <c r="N51" s="37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="37"/>
+      <c r="B52" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="37">
+        <v>1</v>
+      </c>
+      <c r="H52" s="37">
+        <v>9</v>
+      </c>
+      <c r="I52" s="37">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="J52" s="24">
+        <v>25</v>
+      </c>
+      <c r="K52" s="13">
+        <f t="shared" si="10"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="L52" s="13">
+        <f t="shared" si="11"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="M52" s="37"/>
+      <c r="N52" s="37" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" s="66" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="64"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="64"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="64"/>
+      <c r="N53" s="64"/>
+    </row>
+    <row r="54" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="38"/>
+      <c r="B54" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="41"/>
-    </row>
-    <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="42"/>
-      <c r="B53" s="61" t="s">
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
+      <c r="N54" s="41"/>
+    </row>
+    <row r="55" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="42"/>
+      <c r="B55" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C55" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="26"/>
-      <c r="E53" s="61" t="s">
+      <c r="D55" s="26"/>
+      <c r="E55" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="61" t="s">
+      <c r="F55" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="61" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="25"/>
-      <c r="B54" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="61" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -2990,10 +3113,10 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -3008,129 +3131,133 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="43"/>
-      <c r="B59" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="43"/>
-      <c r="J59" s="43"/>
-      <c r="K59" s="43"/>
-      <c r="L59" s="43"/>
-      <c r="M59" s="43"/>
-      <c r="N59" s="43"/>
-    </row>
-    <row r="60" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="44"/>
-      <c r="B60" s="51" t="s">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="17"/>
+      <c r="B59" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="17"/>
+      <c r="B60" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+    </row>
+    <row r="61" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="43"/>
+      <c r="B61" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="43"/>
+      <c r="G61" s="43"/>
+      <c r="H61" s="43"/>
+      <c r="I61" s="43"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+      <c r="L61" s="43"/>
+      <c r="M61" s="43"/>
+      <c r="N61" s="43"/>
+    </row>
+    <row r="62" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="44"/>
+      <c r="B62" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="45"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="62"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="62"/>
-      <c r="J60" s="62"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="62"/>
-      <c r="M60" s="62"/>
-      <c r="N60" s="63"/>
-    </row>
-    <row r="61" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="46"/>
-      <c r="B61" s="14" t="s">
+      <c r="C62" s="45"/>
+      <c r="D62" s="62"/>
+      <c r="E62" s="62"/>
+      <c r="F62" s="62"/>
+      <c r="G62" s="62"/>
+      <c r="H62" s="62"/>
+      <c r="I62" s="62"/>
+      <c r="J62" s="62"/>
+      <c r="K62" s="62"/>
+      <c r="L62" s="62"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="63"/>
+    </row>
+    <row r="63" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="46"/>
+      <c r="B63" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C63" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14" t="s">
+      <c r="D63" s="14"/>
+      <c r="E63" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F63" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G63" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="14" t="s">
+      <c r="H63" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="I63" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="J63" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="K61" s="14" t="s">
+      <c r="K63" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="L61" s="14" t="s">
+      <c r="L63" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="27"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M63" s="14"/>
+      <c r="N63" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="27"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27"/>
+      <c r="K64" s="27"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -3146,7 +3273,7 @@
       <c r="M65" s="18"/>
       <c r="N65" s="18"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
@@ -3162,7 +3289,7 @@
       <c r="M66" s="18"/>
       <c r="N66" s="18"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -3178,7 +3305,7 @@
       <c r="M67" s="18"/>
       <c r="N67" s="18"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -3194,7 +3321,7 @@
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -3210,7 +3337,7 @@
       <c r="M69" s="18"/>
       <c r="N69" s="18"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="18"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -3226,7 +3353,7 @@
       <c r="M70" s="18"/>
       <c r="N70" s="18"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="18"/>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -3242,7 +3369,7 @@
       <c r="M71" s="18"/>
       <c r="N71" s="18"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="18"/>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -3257,6 +3384,38 @@
       <c r="L72" s="18"/>
       <c r="M72" s="18"/>
       <c r="N72" s="18"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3291,17 +3450,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B51EC7ECFAC78D4E8EF6CBAFFF0B3505" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5c1b9c823c4c056c7e05980495393fcd">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf9f6c1f-8ad0-4eb8-bb2b-fb0b622a341e" xmlns:ns3="72c39c84-b0a3-45a2-a38c-ff46bb47f11f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="432eb190a40d519ccc5fb67819ee5399" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B51EC7ECFAC78D4E8EF6CBAFFF0B3505" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5d9401e09799b0dc5f93c06ba9768007">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf9f6c1f-8ad0-4eb8-bb2b-fb0b622a341e" xmlns:ns3="72c39c84-b0a3-45a2-a38c-ff46bb47f11f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="70cec36318042db763ca353140da6103" ns2:_="" ns3:_="">
     <xsd:import namespace="cf9f6c1f-8ad0-4eb8-bb2b-fb0b622a341e"/>
     <xsd:import namespace="72c39c84-b0a3-45a2-a38c-ff46bb47f11f"/>
     <xsd:element name="properties">
@@ -3554,6 +3704,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3566,15 +3725,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4740145F-09D2-466B-B9A2-2798696B0ADF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B62755-DD8A-4807-9D30-E98C725A4607}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D22CE84D-5819-46BA-9024-526A9CB2683F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -3592,6 +3743,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4740145F-09D2-466B-B9A2-2798696B0ADF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4958292-C6C4-482B-887A-6CF9FB19AB74}">
   <ds:schemaRefs>

--- a/Documentation/Working_Documents/Chatterbox_BOM.xlsx
+++ b/Documentation/Working_Documents/Chatterbox_BOM.xlsx
@@ -1433,7 +1433,7 @@
       <c r="M16" s="68" t="n"/>
       <c r="N16" s="74" t="inlineStr">
         <is>
-          <t>https://www.digikey.ca/en/products/detail/c-k/os102011ma1qs1/1981431</t>
+          <t>https://www.digikey.ca/en/products/detail/c-k/os102011ma1qn1/1981430</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       <c r="M28" s="68" t="n"/>
       <c r="N28" s="74" t="inlineStr">
         <is>
-          <t>https://www.digikey.ca/en/products/detail/c-k/os103011ma7qp1/1981432</t>
+          <t>https://www.digikey.ca/en/products/detail/c-k/os103011ma7qp1c/10063872</t>
         </is>
       </c>
     </row>
